--- a/data/gravel/Surly Crosscheck 2025.xlsx
+++ b/data/gravel/Surly Crosscheck 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5228DBD6-F2F5-B14E-8127-7F282D0781FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A471D63-CDEB-A440-8B0A-EA1C03FA6355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2920" yWindow="1200" windowWidth="25720" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -760,7 +760,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>2025</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="4" spans="1:61" x14ac:dyDescent="0.3">

--- a/data/gravel/Surly Crosscheck 2025.xlsx
+++ b/data/gravel/Surly Crosscheck 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A471D63-CDEB-A440-8B0A-EA1C03FA6355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD387568-FBF2-0647-94D1-D01A940A47E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2920" yWindow="1200" windowWidth="25720" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -369,13 +369,16 @@
   </si>
   <si>
     <t>a8:l34</t>
+  </si>
+  <si>
+    <t>https://surlybikes.com/cdn/shop/files/CrossCheck_BK0274.jpg?v=1747923766&amp;width=823</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -407,6 +410,13 @@
       <color rgb="FF757575"/>
       <name val="Futura Medium"/>
     </font>
+    <font>
+      <u/>
+      <sz val="14"/>
+      <color theme="10"/>
+      <name val="Futura"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -425,10 +435,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -436,8 +447,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -779,6 +792,11 @@
         <v>108</v>
       </c>
     </row>
+    <row r="6" spans="1:61" x14ac:dyDescent="0.3">
+      <c r="B6" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
     <row r="7" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>5</v>
@@ -2082,6 +2100,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{905DCAA8-7C1E-304F-8BE7-A4FB0E211E7B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/data/gravel/Surly Crosscheck 2025.xlsx
+++ b/data/gravel/Surly Crosscheck 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD387568-FBF2-0647-94D1-D01A940A47E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EEFA10E-E534-5742-8635-5CEDF65616ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2920" yWindow="1200" windowWidth="25720" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -372,6 +372,12 @@
   </si>
   <si>
     <t>https://surlybikes.com/cdn/shop/files/CrossCheck_BK0274.jpg?v=1747923766&amp;width=823</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Bloomington, Minnesota, USA</t>
   </si>
 </sst>
 </file>
@@ -745,7 +751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BI74"/>
+  <dimension ref="A1:BI75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -2049,54 +2055,62 @@
         <v>55</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>65</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Surly Crosscheck 2025.xlsx
+++ b/data/gravel/Surly Crosscheck 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EEFA10E-E534-5742-8635-5CEDF65616ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4950264B-DFBC-8E48-90F6-887966652045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2920" yWindow="1200" windowWidth="25720" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="121">
   <si>
     <t>brand</t>
   </si>
@@ -378,6 +378,24 @@
   </si>
   <si>
     <t>Bloomington, Minnesota, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -751,7 +769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BI75"/>
+  <dimension ref="A1:BI81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1981,135 +1999,165 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53" s="1">
-        <v>27.2</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>46</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B59" s="1">
+        <v>27.2</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="1" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="1" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="1" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="1" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="1" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="1" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="1" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="1" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="1" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="1" t="s">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="1" t="s">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B81" s="1" t="s">
         <v>114</v>
       </c>
     </row>
